--- a/modelos_x_cliente/COFCO.xlsx
+++ b/modelos_x_cliente/COFCO.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\Documents\LEONARDO\Gerador-de-fichas-de-EPI\modelos_x_cliente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo GAP\Documents\Gerador-de-fichas-de-EPI\modelos_x_cliente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08381A52-7EB0-46DF-B5E7-1164C6596797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B6D16C-3984-4C3F-BE7F-D75DBE51948A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COFCO" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>Supervisor Técnico de Campo</t>
   </si>
@@ -109,26 +109,10 @@
     <t>Relação de Uniformes/EPIs</t>
   </si>
   <si>
-    <t>Jaqueta de Frio</t>
-  </si>
-  <si>
-    <t>Boné Árabe - Caqui (Reptec)</t>
-  </si>
-  <si>
     <t>Óculos Espelhado (Steelpro - Aero)</t>
   </si>
   <si>
     <t>Mochila de EPI`s GAP (LH Brindes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela Plástica para Boné Árabe </t>
-  </si>
-  <si>
-    <t>sob 
-solicitação</t>
-  </si>
-  <si>
-    <t>Dow site</t>
   </si>
   <si>
     <t>Técnica (Serviço de Saúde)
@@ -158,9 +142,6 @@
   </si>
   <si>
     <t xml:space="preserve">ENVIO DE NOTEBOOK ? </t>
-  </si>
-  <si>
-    <t>G</t>
   </si>
   <si>
     <t>TICKET LOG</t>
@@ -380,7 +361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -667,19 +648,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -928,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -950,18 +918,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1026,18 +982,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1047,22 +994,22 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1071,29 +1018,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1105,52 +1049,49 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1162,16 +1103,61 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1185,81 +1171,36 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1568,7 +1509,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:Z34"/>
+  <dimension ref="B2:Z30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.28515625" style="1" customWidth="1"/>
@@ -1593,21 +1534,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="94" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
+      <c r="B2" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -1622,861 +1563,695 @@
     </row>
     <row r="3" spans="2:26" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:26" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="100" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="104" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="87" t="s">
+      <c r="B4" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="98" t="s">
+      <c r="C4" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="81" t="s">
+      <c r="G4" s="70"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="82"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="81" t="s">
+      <c r="J4" s="79"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="82"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="78" t="s">
+      <c r="M4" s="79"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="81" t="s">
+      <c r="P4" s="86"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="S4" s="82"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="84" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" s="82"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="83"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="79"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="80"/>
     </row>
     <row r="5" spans="2:26" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="101"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="11" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="13" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="14" t="s">
+      <c r="O5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="U5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="X5" s="11" t="s">
+      <c r="X5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="Y5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Z5" s="13" t="s">
+      <c r="Z5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="102">
+      <c r="B6" s="76">
         <v>3</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="35">
         <v>3</v>
       </c>
-      <c r="D6" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="75" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="19"/>
+      <c r="D6" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="16"/>
     </row>
-    <row r="7" spans="2:26" ht="27" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="103"/>
-      <c r="C7" s="48">
+    <row r="7" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="77"/>
+      <c r="C7" s="37">
         <v>1</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="25"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="7"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="22"/>
     </row>
     <row r="8" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="103"/>
-      <c r="C8" s="43">
+      <c r="B8" s="77"/>
+      <c r="C8" s="37">
         <v>1</v>
       </c>
-      <c r="D8" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="23"/>
+      <c r="D8" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="20"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="25"/>
+      <c r="H8" s="22"/>
       <c r="I8" s="6"/>
       <c r="J8" s="4"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="28"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
       <c r="R8" s="6"/>
       <c r="S8" s="4"/>
       <c r="T8" s="7"/>
       <c r="U8" s="6"/>
       <c r="V8" s="4"/>
       <c r="W8" s="7"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="25"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="22"/>
     </row>
     <row r="9" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="103"/>
-      <c r="C9" s="43">
-        <v>1</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="23"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="37">
+        <v>2</v>
+      </c>
+      <c r="D9" s="38">
+        <v>40</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="20"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="25"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="22"/>
     </row>
     <row r="10" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="103"/>
-      <c r="C10" s="43">
-        <v>2</v>
-      </c>
-      <c r="D10" s="44">
-        <v>40</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="25"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="39">
+        <v>1</v>
+      </c>
+      <c r="D10" s="58">
+        <v>37</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="30"/>
     </row>
-    <row r="11" spans="2:26" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="103"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="T11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U11" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="V11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="W11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="X11" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y11" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z11" s="31" t="s">
-        <v>29</v>
-      </c>
+    <row r="11" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="55"/>
+      <c r="C11" s="59">
+        <v>1</v>
+      </c>
+      <c r="D11" s="63">
+        <v>0</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="30"/>
     </row>
     <row r="12" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="103"/>
-      <c r="C12" s="45">
+      <c r="B12" s="55"/>
+      <c r="C12" s="60">
         <v>1</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="64"/>
+      <c r="E12" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="29"/>
+      <c r="Z12" s="30"/>
+    </row>
+    <row r="13" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="55"/>
+      <c r="C13" s="61">
+        <v>1</v>
+      </c>
+      <c r="D13" s="65"/>
+      <c r="E13" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="30"/>
+    </row>
+    <row r="14" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="89" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="59">
+        <v>1</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="20"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="22"/>
+    </row>
+    <row r="15" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="90"/>
+      <c r="C15" s="62">
+        <v>1</v>
+      </c>
+      <c r="D15" s="63"/>
+      <c r="E15" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="20"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="7"/>
+    </row>
+    <row r="16" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="90"/>
+      <c r="C16" s="62">
+        <v>1</v>
+      </c>
+      <c r="D16" s="63"/>
+      <c r="E16" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="20"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="7"/>
+    </row>
+    <row r="17" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="90"/>
+      <c r="C17" s="62">
+        <v>1</v>
+      </c>
+      <c r="D17" s="63"/>
+      <c r="E17" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="22"/>
+    </row>
+    <row r="18" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="90"/>
+      <c r="C18" s="62">
+        <v>1</v>
+      </c>
+      <c r="D18" s="63"/>
+      <c r="E18" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="20"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="22"/>
+    </row>
+    <row r="19" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="90"/>
+      <c r="C19" s="62">
+        <v>1</v>
+      </c>
+      <c r="D19" s="63"/>
+      <c r="E19" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="20"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="22"/>
+    </row>
+    <row r="20" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="42"/>
+      <c r="C20" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="94"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="Z20" s="44"/>
+    </row>
+    <row r="21" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="42"/>
+      <c r="C21" s="93" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="94"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="36"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="Z21" s="44"/>
     </row>
-    <row r="13" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="63"/>
-      <c r="C13" s="67">
-        <v>1</v>
-      </c>
-      <c r="D13" s="71">
-        <v>0</v>
-      </c>
-      <c r="E13" s="58" t="s">
+    <row r="22" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="42"/>
+      <c r="C22" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="94"/>
+      <c r="E22" s="95"/>
+      <c r="G22" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="Z22" s="44"/>
+    </row>
+    <row r="23" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="42"/>
+      <c r="C23" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="96"/>
+      <c r="E23" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="47"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="Z23" s="44"/>
+    </row>
+    <row r="24" spans="2:26" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="36"/>
+      <c r="F24" s="97"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="34"/>
     </row>
-    <row r="14" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="63"/>
-      <c r="C14" s="68">
-        <v>1</v>
-      </c>
-      <c r="D14" s="72"/>
-      <c r="E14" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="37"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="36"/>
+    <row r="25" spans="2:26" ht="21" x14ac:dyDescent="0.25">
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="46"/>
     </row>
-    <row r="15" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="63"/>
-      <c r="C15" s="69">
-        <v>1</v>
-      </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="64" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="37"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="37"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="36"/>
-    </row>
-    <row r="16" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="67">
-        <v>1</v>
-      </c>
-      <c r="D16" s="71"/>
-      <c r="E16" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="25"/>
-    </row>
-    <row r="17" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="86"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="7"/>
-    </row>
-    <row r="18" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="86"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="25"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="7"/>
-    </row>
-    <row r="19" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="86"/>
-      <c r="C19" s="70">
-        <v>1</v>
-      </c>
-      <c r="D19" s="71"/>
-      <c r="E19" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="25"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="7"/>
-    </row>
-    <row r="20" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="86"/>
-      <c r="C20" s="70">
-        <v>1</v>
-      </c>
-      <c r="D20" s="71"/>
-      <c r="E20" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="25"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="7"/>
-    </row>
-    <row r="21" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="86"/>
-      <c r="C21" s="70">
-        <v>1</v>
-      </c>
-      <c r="D21" s="71"/>
-      <c r="E21" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="25"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="25"/>
-    </row>
-    <row r="22" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="86"/>
-      <c r="C22" s="70">
-        <v>1</v>
-      </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="25"/>
-    </row>
-    <row r="23" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="86"/>
-      <c r="C23" s="70">
-        <v>1</v>
-      </c>
-      <c r="D23" s="71"/>
-      <c r="E23" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="25"/>
-    </row>
-    <row r="24" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="49"/>
-      <c r="C24" s="89" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="O24" s="50"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="50"/>
-      <c r="Z24" s="51"/>
-    </row>
-    <row r="25" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="49"/>
-      <c r="C25" s="89" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="90"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="O25" s="50"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="50"/>
-      <c r="Z25" s="51"/>
-    </row>
-    <row r="26" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="49"/>
-      <c r="C26" s="89" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="90"/>
-      <c r="E26" s="91"/>
-      <c r="G26" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="O26" s="50"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="Z26" s="51"/>
-    </row>
-    <row r="27" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="49"/>
-      <c r="C27" s="92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="92"/>
-      <c r="E27" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="54"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="Z27" s="51"/>
-    </row>
-    <row r="28" spans="2:26" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="76" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="93" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="39"/>
-      <c r="W28" s="39"/>
-      <c r="X28" s="39"/>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="40"/>
-    </row>
-    <row r="29" spans="2:26" ht="21" x14ac:dyDescent="0.25">
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="53"/>
-    </row>
-    <row r="31" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0"/>
   <mergeCells count="20">
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E24:G24"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B12"/>
+    <mergeCell ref="B6:B10"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E28:G28"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2485,15 +2260,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a415345-6a39-4751-b960-4fc8f12baef7">
@@ -2503,6 +2269,15 @@
     <MediaLengthInSeconds xmlns="3a415345-6a39-4751-b960-4fc8f12baef7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2747,20 +2522,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A9F4E51-4DE3-4214-9644-9D529D38719F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6192A4F-43EB-47CE-AABA-403827665463}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3a415345-6a39-4751-b960-4fc8f12baef7"/>
     <ds:schemaRef ds:uri="74ad866f-79dd-4f7a-ba3c-81e3e663768c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A9F4E51-4DE3-4214-9644-9D529D38719F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
